--- a/product_release/work_items/financial-analysis/SpeakSharp_Updated_Financial_Model_2026-10-12.xlsx
+++ b/product_release/work_items/financial-analysis/SpeakSharp_Updated_Financial_Model_2026-10-12.xlsx
@@ -9559,7 +9559,7 @@
     </row>
     <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="115" t="str">
-        <f aca="false">IF(COUNTIF(F5:F15,"FAIL")+COUNTIF(F20:F35,"FAIL")=0,"MODEL STATUS: PASS","MODEL STATUS: FAIL")</f>
+        <f>IF(AND(COUNTIF(F5:F15,"OK")=ROWS(F5:F15),COUNTIF(F20:F35,"OK")=ROWS(F20:F35)),"MODEL STATUS: PASS","MODEL STATUS: FAIL")</f>
         <v>MODEL STATUS: PASS</v>
       </c>
       <c r="B18" s="115"/>
